--- a/grid-trading-dashboard/data/512980-梅梅.xlsx
+++ b/grid-trading-dashboard/data/512980-梅梅.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\caojingwen\obsidian\cjwagents\grid-trading-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6412C5FF-2DF4-4D3A-8A68-E0EA91E4F2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A6A221-6F9B-4BCE-88C9-7D81B224940F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="27630" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>字段</t>
   </si>
@@ -101,6 +101,10 @@
   </si>
   <si>
     <t>512980</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖出</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -620,7 +624,7 @@
         <v>0.77700000000000002</v>
       </c>
       <c r="F2" s="4">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -630,10 +634,30 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.19</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="3"/>
